--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate/AGGREGATE_CIUDAD MOLINA BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate/AGGREGATE_CIUDAD MOLINA BASKET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE68"/>
+  <dimension ref="A1:BA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,81 +639,6 @@
           <t>Gen/TO</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 37</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 38</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 40</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 41</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 42</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 43</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 44</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 45</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 46</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 47</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 48</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 49</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 50</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 51</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -722,16 +647,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2009.76</v>
+        <v>1968.76</v>
       </c>
       <c r="C2" t="n">
-        <v>2011.22</v>
+        <v>1974.72</v>
       </c>
       <c r="D2" t="n">
-        <v>95.31528127206371</v>
+        <v>97.07705396208068</v>
       </c>
       <c r="E2" t="n">
-        <v>106.8008472469446</v>
+        <v>108.7749149246475</v>
       </c>
       <c r="F2" t="n">
         <v>0.43810888252149</v>
@@ -740,19 +665,19 @@
         <v>0.1518390336590662</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3096085409252669</v>
+        <v>0.3433362753751103</v>
       </c>
       <c r="I2" t="n">
         <v>0.2223495702005731</v>
       </c>
       <c r="J2" t="n">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="K2" t="n">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="L2" t="n">
-        <v>346</v>
+        <v>268</v>
       </c>
       <c r="M2" t="n">
         <v>152</v>
@@ -827,13 +752,13 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.692722371967655</v>
+        <v>0.628032345013477</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8189655172413793</v>
+        <v>0.493573264781491</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.947945205479452</v>
+        <v>1.786666666666667</v>
       </c>
       <c r="AN2" t="n">
         <v>1.11731843575419</v>
@@ -843,51 +768,6 @@
       </c>
       <c r="AP2" t="n">
         <v>5.991620111731844</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -897,16 +777,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.29846153846155</v>
+        <v>75.72153846153846</v>
       </c>
       <c r="C3" t="n">
-        <v>77.3546153846154</v>
+        <v>75.95076923076924</v>
       </c>
       <c r="D3" t="n">
-        <v>95.3152812720637</v>
+        <v>97.07705396208068</v>
       </c>
       <c r="E3" t="n">
-        <v>106.8008472469446</v>
+        <v>108.7749149246475</v>
       </c>
       <c r="F3" t="n">
         <v>0.43810888252149</v>
@@ -915,19 +795,19 @@
         <v>0.1518390336590662</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3096085409252669</v>
+        <v>0.3433362753751103</v>
       </c>
       <c r="I3" t="n">
         <v>0.2223495702005731</v>
       </c>
       <c r="J3" t="n">
-        <v>9.884615384615385</v>
+        <v>8.961538461538462</v>
       </c>
       <c r="K3" t="n">
-        <v>10.96153846153846</v>
+        <v>7.384615384615385</v>
       </c>
       <c r="L3" t="n">
-        <v>13.30769230769231</v>
+        <v>10.30769230769231</v>
       </c>
       <c r="M3" t="n">
         <v>5.846153846153846</v>
@@ -1002,13 +882,13 @@
         <v>0.8181818181818182</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.692722371967655</v>
+        <v>0.628032345013477</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8189655172413793</v>
+        <v>0.4935732647814911</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9479452054794522</v>
+        <v>1.786666666666667</v>
       </c>
       <c r="AN3" t="n">
         <v>1.11731843575419</v>
@@ -1018,51 +898,6 @@
       </c>
       <c r="AP3" t="n">
         <v>5.991620111731844</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1072,16 +907,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2012.68</v>
+        <v>1980.68</v>
       </c>
       <c r="C4" t="n">
-        <v>2011.22</v>
+        <v>1974.72</v>
       </c>
       <c r="D4" t="n">
-        <v>106.8008472469446</v>
+        <v>108.7749149246475</v>
       </c>
       <c r="E4" t="n">
-        <v>95.31528127206371</v>
+        <v>97.07705396208068</v>
       </c>
       <c r="F4" t="n">
         <v>0.5102409638554217</v>
@@ -1090,19 +925,19 @@
         <v>0.1594546736121856</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3149448345035105</v>
+        <v>0.3502024291497975</v>
       </c>
       <c r="I4" t="n">
         <v>0.2734939759036145</v>
       </c>
       <c r="J4" t="n">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="L4" t="n">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="M4" t="n">
         <v>175</v>
@@ -1177,13 +1012,13 @@
         <v>1.014084507042254</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8128491620111732</v>
+        <v>0.6927374301675978</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8853503184713376</v>
+        <v>0.5404624277456648</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9245283018867925</v>
+        <v>1.904458598726115</v>
       </c>
       <c r="AN4" t="n">
         <v>1.064690026954178</v>
@@ -1193,51 +1028,6 @@
       </c>
       <c r="AP4" t="n">
         <v>5.539083557951482</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1247,16 +1037,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.41076923076922</v>
+        <v>76.17999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>77.3546153846154</v>
+        <v>75.95076923076924</v>
       </c>
       <c r="D5" t="n">
-        <v>106.8008472469446</v>
+        <v>108.7749149246475</v>
       </c>
       <c r="E5" t="n">
-        <v>95.3152812720637</v>
+        <v>97.07705396208068</v>
       </c>
       <c r="F5" t="n">
         <v>0.5102409638554217</v>
@@ -1265,19 +1055,19 @@
         <v>0.1594546736121856</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3149448345035105</v>
+        <v>0.3502024291497976</v>
       </c>
       <c r="I5" t="n">
         <v>0.2734939759036144</v>
       </c>
       <c r="J5" t="n">
-        <v>11.19230769230769</v>
+        <v>9.538461538461538</v>
       </c>
       <c r="K5" t="n">
-        <v>10.69230769230769</v>
+        <v>7.192307692307693</v>
       </c>
       <c r="L5" t="n">
-        <v>15.07692307692308</v>
+        <v>11.5</v>
       </c>
       <c r="M5" t="n">
         <v>6.730769230769231</v>
@@ -1352,13 +1142,13 @@
         <v>1.014084507042254</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8128491620111731</v>
+        <v>0.6927374301675977</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8853503184713375</v>
+        <v>0.5404624277456648</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9245283018867925</v>
+        <v>1.904458598726115</v>
       </c>
       <c r="AN5" t="n">
         <v>1.064690026954178</v>
@@ -1368,51 +1158,6 @@
       </c>
       <c r="AP5" t="n">
         <v>5.539083557951482</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1711,10 +1456,10 @@
         <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>18</v>
@@ -1735,22 +1480,22 @@
         <v>66</v>
       </c>
       <c r="S8" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="U8" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="V8" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -1833,10 +1578,10 @@
         <v>0.27</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
       <c r="BA8" t="n">
         <v>0.027</v>
@@ -1900,10 +1645,10 @@
         <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1912,10 +1657,10 @@
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>2</v>
@@ -2001,7 +1746,7 @@
         <v>0.014</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="BA9" t="n">
         <v>0.02</v>
@@ -2206,10 +1951,10 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
         <v>8</v>
@@ -2218,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
         <v>11</v>
@@ -2230,22 +1975,22 @@
         <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
         <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
         <v>9</v>
@@ -2328,10 +2073,10 @@
         <v>0.166</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1</v>
+        <v>0.114</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.118</v>
+        <v>0.102</v>
       </c>
       <c r="BA11" t="n">
         <v>0.008999999999999999</v>
@@ -2371,10 +2116,10 @@
         <v>107</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
         <v>23</v>
@@ -2383,7 +2128,7 @@
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
         <v>46</v>
@@ -2395,22 +2140,22 @@
         <v>52</v>
       </c>
       <c r="S12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="U12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="X12" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="n">
         <v>23</v>
@@ -2493,10 +2238,10 @@
         <v>0.177</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="BA12" t="n">
         <v>0.176</v>
@@ -2560,10 +2305,10 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2661,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
@@ -2701,10 +2446,10 @@
         <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
         <v>15</v>
@@ -2713,7 +2458,7 @@
         <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>13</v>
@@ -2725,22 +2470,22 @@
         <v>25</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="U14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
         <v>17</v>
@@ -2823,10 +2568,10 @@
         <v>0.18</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="BA14" t="n">
         <v>0.019</v>
@@ -2866,10 +2611,10 @@
         <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M15" t="n">
         <v>12</v>
@@ -2890,22 +2635,22 @@
         <v>53</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
         <v>6</v>
@@ -2988,10 +2733,10 @@
         <v>0.179</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.049</v>
+        <v>0.055</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.082</v>
+        <v>0.076</v>
       </c>
       <c r="BA15" t="n">
         <v>0.018</v>
@@ -3067,10 +2812,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>1</v>
@@ -3156,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -3196,10 +2941,10 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
+        <v>30</v>
+      </c>
+      <c r="L17" t="n">
         <v>33</v>
-      </c>
-      <c r="L17" t="n">
-        <v>30</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
@@ -3208,7 +2953,7 @@
         <v>16</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
         <v>14</v>
@@ -3220,22 +2965,22 @@
         <v>27</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
         <v>31</v>
@@ -3318,10 +3063,10 @@
         <v>0.221</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.123</v>
+        <v>0.135</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.153</v>
+        <v>0.14</v>
       </c>
       <c r="BA17" t="n">
         <v>0.01</v>
@@ -3385,10 +3130,10 @@
         <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3397,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3486,7 +3231,7 @@
         <v>0.038</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.257</v>
+        <v>0.26</v>
       </c>
       <c r="BA18" t="n">
         <v>0.002</v>
@@ -3526,10 +3271,10 @@
         <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
         <v>14</v>
@@ -3538,7 +3283,7 @@
         <v>13</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
         <v>45</v>
@@ -3550,22 +3295,22 @@
         <v>71</v>
       </c>
       <c r="S19" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="U19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V19" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="W19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
         <v>41</v>
@@ -3648,10 +3393,10 @@
         <v>0.219</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.073</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.202</v>
+        <v>0.187</v>
       </c>
       <c r="BA19" t="n">
         <v>0.039</v>
@@ -3691,10 +3436,10 @@
         <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
         <v>9</v>
@@ -3715,22 +3460,22 @@
         <v>36</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="U20" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="V20" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
         <v>16</v>
@@ -3813,10 +3558,10 @@
         <v>0.191</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.179</v>
+        <v>0.169</v>
       </c>
       <c r="BA20" t="n">
         <v>0.023</v>
@@ -3856,10 +3601,10 @@
         <v>16</v>
       </c>
       <c r="K21" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M21" t="n">
         <v>12</v>
@@ -3880,22 +3625,22 @@
         <v>25</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -3978,10 +3723,10 @@
         <v>0.099</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.058</v>
+        <v>0.068</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.147</v>
+        <v>0.136</v>
       </c>
       <c r="BA21" t="n">
         <v>0.025</v>
@@ -4021,10 +3766,10 @@
         <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M22" t="n">
         <v>20</v>
@@ -4033,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
         <v>41</v>
@@ -4045,22 +3790,22 @@
         <v>37</v>
       </c>
       <c r="S22" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="U22" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="V22" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W22" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="X22" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="Y22" t="n">
         <v>37</v>
@@ -4143,10 +3888,10 @@
         <v>0.236</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.109</v>
+        <v>0.104</v>
       </c>
       <c r="BA22" t="n">
         <v>0.066</v>
@@ -4186,10 +3931,10 @@
         <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M23" t="n">
         <v>4</v>
@@ -4210,22 +3955,22 @@
         <v>48</v>
       </c>
       <c r="S23" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
         <v>35</v>
@@ -4308,10 +4053,10 @@
         <v>0.196</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.061</v>
+        <v>0.075</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.144</v>
+        <v>0.129</v>
       </c>
       <c r="BA23" t="n">
         <v>0.01</v>
@@ -4320,331 +4065,331 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#88 J. TAVELLI</t>
+          <t>#37 C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>26</v>
       </c>
       <c r="C24" t="n">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="D24" t="n">
+        <v>77</v>
+      </c>
+      <c r="E24" t="n">
+        <v>141</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>42</v>
+      </c>
+      <c r="H24" t="n">
+        <v>54</v>
+      </c>
+      <c r="I24" t="n">
+        <v>88</v>
+      </c>
+      <c r="J24" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" t="n">
+        <v>77</v>
+      </c>
+      <c r="L24" t="n">
+        <v>82</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>17</v>
+      </c>
+      <c r="R24" t="n">
+        <v>75</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>194</v>
+      </c>
+      <c r="U24" t="n">
+        <v>33</v>
+      </c>
+      <c r="V24" t="n">
         <v>45</v>
       </c>
-      <c r="E24" t="n">
-        <v>96</v>
-      </c>
-      <c r="F24" t="n">
-        <v>13</v>
-      </c>
-      <c r="G24" t="n">
-        <v>63</v>
-      </c>
-      <c r="H24" t="n">
-        <v>38</v>
-      </c>
-      <c r="I24" t="n">
-        <v>53</v>
-      </c>
-      <c r="J24" t="n">
-        <v>100</v>
-      </c>
-      <c r="K24" t="n">
-        <v>62</v>
-      </c>
-      <c r="L24" t="n">
-        <v>14</v>
-      </c>
-      <c r="M24" t="n">
-        <v>40</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="W24" t="n">
+        <v>41</v>
+      </c>
+      <c r="X24" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>116</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AB24" t="n">
         <v>5</v>
       </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>11</v>
-      </c>
-      <c r="R24" t="n">
-        <v>72</v>
-      </c>
-      <c r="S24" t="n">
-        <v>51</v>
-      </c>
-      <c r="T24" t="n">
-        <v>207</v>
-      </c>
-      <c r="U24" t="n">
-        <v>31</v>
-      </c>
-      <c r="V24" t="n">
-        <v>19</v>
-      </c>
-      <c r="W24" t="n">
-        <v>37</v>
-      </c>
-      <c r="X24" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13</v>
-      </c>
       <c r="AC24" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.448</v>
+        <v>0.312</v>
       </c>
       <c r="AE24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.235</v>
+        <v>0.333</v>
       </c>
       <c r="AH24" t="n">
         <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AL24" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.17</v>
+        <v>0.227</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>501:59</t>
+          <t>619:22</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>225.32</v>
+        <v>254.72</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.406</v>
+        <v>0.495</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.458</v>
+        <v>0.53</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.741</v>
+        <v>0.923</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.191</v>
+        <v>0.13</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.239</v>
+        <v>0.295</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.326</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.698</v>
+        <v>5.545</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.023</v>
+        <v>6.485</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.202</v>
+        <v>0.185</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.026</v>
+        <v>0.124</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.131</v>
+        <v>0.133</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.166</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#88 J. TAVELLI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>26</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="L25" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>501:59</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>225.32</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>0.741</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.326</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.698</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>6.023</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="26">
@@ -4681,10 +4426,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4696,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -4773,7 +4518,7 @@
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -4846,10 +4591,10 @@
         <v>400</v>
       </c>
       <c r="K27" t="n">
-        <v>683</v>
+        <v>642</v>
       </c>
       <c r="L27" t="n">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="M27" t="n">
         <v>196</v>
@@ -4858,7 +4603,7 @@
         <v>61</v>
       </c>
       <c r="O27" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P27" t="n">
         <v>358</v>
@@ -4870,22 +4615,22 @@
         <v>614</v>
       </c>
       <c r="S27" t="n">
-        <v>542</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1761</v>
+        <v>1220</v>
       </c>
       <c r="U27" t="n">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="V27" t="n">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="W27" t="n">
-        <v>346</v>
+        <v>268</v>
       </c>
       <c r="X27" t="n">
-        <v>365</v>
+        <v>150</v>
       </c>
       <c r="Y27" t="n">
         <v>340</v>
@@ -4968,10 +4713,10 @@
         <v>0.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.062</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.137</v>
+        <v>0.13</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
@@ -5011,10 +4756,10 @@
         <v>395</v>
       </c>
       <c r="K28" t="n">
-        <v>776</v>
+        <v>744</v>
       </c>
       <c r="L28" t="n">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="M28" t="n">
         <v>206</v>
@@ -5023,7 +4768,7 @@
         <v>57</v>
       </c>
       <c r="O28" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P28" t="n">
         <v>371</v>
@@ -5035,22 +4780,22 @@
         <v>553</v>
       </c>
       <c r="S28" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2257</v>
+        <v>1653</v>
       </c>
       <c r="U28" t="n">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="V28" t="n">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="W28" t="n">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="X28" t="n">
-        <v>424</v>
+        <v>157</v>
       </c>
       <c r="Y28" t="n">
         <v>317</v>
@@ -5133,10 +4878,10 @@
         <v>0.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
       <c r="BA28" t="n">
         <v>0</v>
@@ -5145,341 +4890,235 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LOBE HUESCA LA MAGIA</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>13</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>AMICS CASTELLÓ</t>
+          <t>#5 A. DUVAL (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>9.423</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2.654</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>6.538</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.577</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.462</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.538</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.346</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.692</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.731</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.296</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.192</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>3.808</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>11.198</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>0.841</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>9.958</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>10.625</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>BIELE ISB</t>
+          <t>#7 A. LUGO NITSCHE (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5594,7 +5233,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AO31" t="n">
@@ -5640,509 +5279,509 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>C.B. GETAFE</t>
+          <t>#7 J. CASCALES FERNANDEZ (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C32" t="n">
-        <v>235</v>
+        <v>0.533</v>
       </c>
       <c r="D32" t="n">
-        <v>77</v>
+        <v>0.133</v>
       </c>
       <c r="E32" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>42</v>
+        <v>0.267</v>
       </c>
       <c r="H32" t="n">
-        <v>54</v>
+        <v>0.267</v>
       </c>
       <c r="I32" t="n">
-        <v>88</v>
+        <v>0.533</v>
       </c>
       <c r="J32" t="n">
-        <v>31</v>
+        <v>0.867</v>
       </c>
       <c r="K32" t="n">
-        <v>88</v>
+        <v>0.4</v>
       </c>
       <c r="L32" t="n">
-        <v>71</v>
+        <v>0.067</v>
       </c>
       <c r="M32" t="n">
-        <v>9</v>
+        <v>0.267</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>33</v>
+        <v>0.267</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>0.067</v>
       </c>
       <c r="R32" t="n">
-        <v>75</v>
+        <v>0.6</v>
       </c>
       <c r="S32" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>269</v>
+        <v>-4</v>
       </c>
       <c r="U32" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>64</v>
+        <v>0.133</v>
       </c>
       <c r="W32" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>69</v>
+        <v>0.133</v>
       </c>
       <c r="Z32" t="n">
-        <v>116</v>
+        <v>0.733</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.595</v>
+        <v>0.182</v>
       </c>
       <c r="AB32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>16</v>
+        <v>0.067</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>20</v>
+        <v>0.133</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>22</v>
+        <v>0.133</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.227</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>619:22</t>
+          <t>04:23</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>254.72</v>
+        <v>1.768</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.495</v>
+        <v>0.105</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.53</v>
+        <v>0.178</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.923</v>
+        <v>0.302</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.13</v>
+        <v>0.151</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.295</v>
+        <v>0.211</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.9389999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.545</v>
+        <v>4.75</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.485</v>
+        <v>8</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.185</v>
+        <v>0.181</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.108</v>
+        <v>0.014</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.151</v>
+        <v>0.098</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.054</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>C.B. STARLABS MORÓN</t>
+          <t>#8 G. CADME ARIAS (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>3.733</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.733</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.533</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>4.627</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>0.454</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>4.909</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>5.455</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>CLASS BASQUET SANT ANTONI</t>
+          <t>#9 R. TIMONER GIMENEZ (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>6.462</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2.923</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3.538</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.615</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>4.115</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1.962</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.769</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.885</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.769</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>9.331</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.326</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>3.652</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>5.978</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>COTO CÓRDOBA CB</t>
+          <t>#10 A. LÓPEZ MARTINEZ (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -6151,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -6166,13 +5805,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -6187,13 +5826,13 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -6235,39 +5874,39 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:37</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS35" t="n">
         <v>0</v>
@@ -6285,13 +5924,13 @@
         <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="BA35" t="n">
         <v>0</v>
@@ -6300,595 +5939,701 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
+          <t>#11 P. CAMPENY LLOVERAS (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>5.889</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1.222</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2.833</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.722</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.944</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1.722</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.389</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>0.944</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.556</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.111</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.611</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>6.742</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.489</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>0.873</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>7.692</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>8.615</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
+          <t>#12 R. MARTÍNEZ-QUINTANILLA JIMÉNEZ (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>25</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>13</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>5.155</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.446</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>5.737</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>6.316</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
+          <t>#13 P. PARRA GOMEZ (Per Game)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#5 A. DUVAL (Per Game)</t>
+          <t>#14 H. KABASELE KASONGA (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C39" t="n">
-        <v>9.423</v>
+        <v>8.667</v>
       </c>
       <c r="D39" t="n">
-        <v>0.923</v>
+        <v>3.667</v>
       </c>
       <c r="E39" t="n">
-        <v>2.654</v>
+        <v>7.167</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>6.538</v>
+        <v>0.083</v>
       </c>
       <c r="H39" t="n">
-        <v>1.577</v>
+        <v>1.333</v>
       </c>
       <c r="I39" t="n">
-        <v>2.462</v>
+        <v>2.25</v>
       </c>
       <c r="J39" t="n">
-        <v>0.615</v>
+        <v>0.5</v>
       </c>
       <c r="K39" t="n">
-        <v>1.346</v>
+        <v>2.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0.385</v>
+        <v>2.75</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.417</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>0.923</v>
+        <v>1.167</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.231</v>
+        <v>0.667</v>
       </c>
       <c r="R39" t="n">
-        <v>2.538</v>
+        <v>2.25</v>
       </c>
       <c r="S39" t="n">
-        <v>2.231</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="U39" t="n">
-        <v>1.308</v>
+        <v>0.417</v>
       </c>
       <c r="V39" t="n">
-        <v>1.038</v>
+        <v>1.667</v>
       </c>
       <c r="W39" t="n">
-        <v>1.231</v>
+        <v>0.667</v>
       </c>
       <c r="X39" t="n">
-        <v>1.154</v>
+        <v>0.333</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.654</v>
+        <v>2.583</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.692</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.386</v>
+        <v>0.646</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.192</v>
+        <v>0.667</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.615</v>
+        <v>1.667</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.312</v>
+        <v>0.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.077</v>
+        <v>0.417</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.346</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.222</v>
+        <v>0.278</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.731</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.192</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.808</v>
+        <v>0.083</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.313</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>11.198</v>
+        <v>9.407</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.427</v>
+        <v>0.506</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.459</v>
+        <v>0.526</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.841</v>
+        <v>0.921</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.082</v>
+        <v>0.124</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.172</v>
+        <v>0.184</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.667</v>
+        <v>0.429</v>
       </c>
       <c r="AV39" t="n">
-        <v>9.958</v>
+        <v>6.214</v>
       </c>
       <c r="AW39" t="n">
-        <v>10.625</v>
+        <v>6.643</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.27</v>
+        <v>0.221</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.019</v>
+        <v>0.135</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.077</v>
+        <v>0.14</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#7 A. LUGO NITSCHE (Per Game)</t>
+          <t>#15 T. BOUNDI (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6906,13 +6651,13 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6954,13 +6699,13 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6973,26 +6718,26 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>00:46</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.546</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AU40" t="n">
         <v>0</v>
@@ -7004,1274 +6749,1274 @@
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#7 J. CASCALES FERNANDEZ (Per Game)</t>
+          <t>#21 G. MILADINOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C41" t="n">
-        <v>0.533</v>
+        <v>6.731</v>
       </c>
       <c r="D41" t="n">
-        <v>0.133</v>
+        <v>2.5</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>5.577</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="G41" t="n">
-        <v>0.267</v>
+        <v>0.423</v>
       </c>
       <c r="H41" t="n">
-        <v>0.267</v>
+        <v>1.5</v>
       </c>
       <c r="I41" t="n">
-        <v>0.533</v>
+        <v>2.192</v>
       </c>
       <c r="J41" t="n">
-        <v>0.867</v>
+        <v>0.885</v>
       </c>
       <c r="K41" t="n">
-        <v>0.4</v>
+        <v>3.115</v>
       </c>
       <c r="L41" t="n">
-        <v>0.067</v>
+        <v>1.654</v>
       </c>
       <c r="M41" t="n">
-        <v>0.267</v>
+        <v>0.538</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>0.267</v>
+        <v>1.731</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.067</v>
+        <v>0.923</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6</v>
+        <v>2.731</v>
       </c>
       <c r="S41" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="V41" t="n">
-        <v>0.133</v>
+        <v>0.769</v>
       </c>
       <c r="W41" t="n">
-        <v>0.067</v>
+        <v>0.769</v>
       </c>
       <c r="X41" t="n">
-        <v>0.4</v>
+        <v>0.385</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.133</v>
+        <v>1.577</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.733</v>
+        <v>3.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.182</v>
+        <v>0.451</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.067</v>
+        <v>1.615</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AF41" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AM41" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>04:23</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>1.768</v>
+        <v>8.695</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.105</v>
+        <v>0.436</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.178</v>
+        <v>0.483</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.302</v>
+        <v>0.774</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.151</v>
+        <v>0.199</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.211</v>
+        <v>0.25</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.25</v>
+        <v>0.511</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.75</v>
+        <v>3.467</v>
       </c>
       <c r="AW41" t="n">
-        <v>8</v>
+        <v>3.978</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.181</v>
+        <v>0.219</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.014</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.097</v>
+        <v>0.187</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.034</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#8 G. CADME ARIAS (Per Game)</t>
+          <t>#22 M. GARCIA ROSELLO (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
-        <v>3.733</v>
+        <v>8.615</v>
       </c>
       <c r="D42" t="n">
-        <v>0.733</v>
+        <v>1.769</v>
       </c>
       <c r="E42" t="n">
-        <v>1.867</v>
+        <v>3.154</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6</v>
+        <v>1.462</v>
       </c>
       <c r="G42" t="n">
-        <v>1.733</v>
+        <v>4.462</v>
       </c>
       <c r="H42" t="n">
-        <v>0.467</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.667</v>
+        <v>1.385</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4</v>
+        <v>1.077</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4</v>
+        <v>3.385</v>
       </c>
       <c r="L42" t="n">
-        <v>1.333</v>
+        <v>1.154</v>
       </c>
       <c r="M42" t="n">
-        <v>0.533</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0.733</v>
+        <v>0.923</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.4</v>
+        <v>0.154</v>
       </c>
       <c r="R42" t="n">
-        <v>0.8</v>
+        <v>2.769</v>
       </c>
       <c r="S42" t="n">
-        <v>0.533</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="U42" t="n">
-        <v>0.6</v>
+        <v>1.462</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4</v>
+        <v>1.077</v>
       </c>
       <c r="W42" t="n">
-        <v>0.667</v>
+        <v>1.231</v>
       </c>
       <c r="X42" t="n">
-        <v>0.667</v>
+        <v>0.615</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.6</v>
+        <v>1.231</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.267</v>
+        <v>2.077</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.474</v>
+        <v>0.593</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.267</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.133</v>
+        <v>0.154</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.333</v>
+        <v>0.385</v>
       </c>
       <c r="AG42" t="n">
         <v>0.4</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.462</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.357</v>
+        <v>0.211</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.267</v>
+        <v>1.154</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.333</v>
+        <v>0.385</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>4.627</v>
+        <v>9.148</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.454</v>
+        <v>0.52</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.479</v>
+        <v>0.524</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.159</v>
+        <v>0.101</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.13</v>
+        <v>0.091</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.545</v>
+        <v>1.167</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.909</v>
+        <v>8.25</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.455</v>
+        <v>9.417</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.166</v>
+        <v>0.191</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.118</v>
+        <v>0.169</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.017</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#9 R. TIMONER GIMENEZ (Per Game)</t>
+          <t>#24 U. ZAMORA MAÑA (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>6.462</v>
+        <v>3.5</v>
       </c>
       <c r="D43" t="n">
-        <v>1.154</v>
+        <v>0.75</v>
       </c>
       <c r="E43" t="n">
-        <v>2.923</v>
+        <v>1.25</v>
       </c>
       <c r="F43" t="n">
-        <v>0.846</v>
+        <v>0.417</v>
       </c>
       <c r="G43" t="n">
-        <v>3.538</v>
+        <v>2.417</v>
       </c>
       <c r="H43" t="n">
-        <v>1.615</v>
+        <v>0.75</v>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>4.115</v>
+        <v>1.333</v>
       </c>
       <c r="K43" t="n">
-        <v>1.923</v>
+        <v>2.75</v>
       </c>
       <c r="L43" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.583</v>
       </c>
       <c r="M43" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>0.115</v>
+        <v>0.167</v>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.769</v>
+        <v>0.667</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.538</v>
+        <v>0.25</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>2.083</v>
       </c>
       <c r="S43" t="n">
-        <v>2.692</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>195</v>
+        <v>58</v>
       </c>
       <c r="U43" t="n">
-        <v>0.923</v>
+        <v>0.833</v>
       </c>
       <c r="V43" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="W43" t="n">
-        <v>1.115</v>
+        <v>0.333</v>
       </c>
       <c r="X43" t="n">
-        <v>1.846</v>
+        <v>0.167</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.885</v>
+        <v>0.667</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.885</v>
+        <v>0.917</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.469</v>
+        <v>0.727</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.231</v>
+        <v>0.083</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.654</v>
+        <v>0.083</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.353</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.385</v>
+        <v>0.25</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.769</v>
+        <v>0.917</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.3</v>
+        <v>0.273</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.615</v>
+        <v>0.167</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.769</v>
+        <v>1.5</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.222</v>
+        <v>0.111</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>9.331</v>
+        <v>4.773</v>
       </c>
       <c r="AP43" t="n">
         <v>0.375</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.25</v>
+        <v>0.205</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.326</v>
+        <v>2</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.652</v>
+        <v>5.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.978</v>
+        <v>7.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.177</v>
+        <v>0.099</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.028</v>
+        <v>0.068</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.136</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.176</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#10 A. LÓPEZ MARTINEZ (Per Game)</t>
+          <t>#25 F. HERNANDEZ MARTINEZ (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C44" t="n">
-        <v>0.333</v>
+        <v>9.615</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1.885</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>4.154</v>
       </c>
       <c r="F44" t="n">
-        <v>0.111</v>
+        <v>1.231</v>
       </c>
       <c r="G44" t="n">
-        <v>0.222</v>
+        <v>4.769</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2.154</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.154</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="K44" t="n">
-        <v>0.111</v>
+        <v>2.192</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="M44" t="n">
-        <v>0.222</v>
+        <v>0.769</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.577</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0.111</v>
+        <v>1.423</v>
       </c>
       <c r="S44" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.385</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.231</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.308</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.423</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.731</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.111</v>
+        <v>0.538</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.111</v>
+        <v>1.846</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1</v>
+        <v>0.292</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.111</v>
+        <v>2.923</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>01:37</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>0.222</v>
+        <v>11.888</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.75</v>
+        <v>0.418</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.75</v>
+        <v>0.466</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.5</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>0.927</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>5.659</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>6.585</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.062</v>
+        <v>0.236</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.073</v>
+        <v>0.104</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#11 P. CAMPENY LLOVERAS (Per Game)</t>
+          <t>#26 M. MUKENDI MUKENDI (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" t="n">
-        <v>5.889</v>
+        <v>8.234999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>1.222</v>
+        <v>2.471</v>
       </c>
       <c r="E45" t="n">
-        <v>2.833</v>
+        <v>4.941</v>
       </c>
       <c r="F45" t="n">
-        <v>0.833</v>
+        <v>0.059</v>
       </c>
       <c r="G45" t="n">
-        <v>2.722</v>
+        <v>0.294</v>
       </c>
       <c r="H45" t="n">
-        <v>0.944</v>
+        <v>3.118</v>
       </c>
       <c r="I45" t="n">
-        <v>1.056</v>
+        <v>4.235</v>
       </c>
       <c r="J45" t="n">
-        <v>0.667</v>
+        <v>0.353</v>
       </c>
       <c r="K45" t="n">
-        <v>1.778</v>
+        <v>2.294</v>
       </c>
       <c r="L45" t="n">
-        <v>0.444</v>
+        <v>1.529</v>
       </c>
       <c r="M45" t="n">
-        <v>0.833</v>
+        <v>0.235</v>
       </c>
       <c r="N45" t="n">
-        <v>0.111</v>
+        <v>0.824</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>0.722</v>
+        <v>1.235</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.167</v>
+        <v>0.529</v>
       </c>
       <c r="R45" t="n">
-        <v>1.389</v>
+        <v>2.824</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="U45" t="n">
-        <v>0.889</v>
+        <v>0.353</v>
       </c>
       <c r="V45" t="n">
-        <v>0.556</v>
+        <v>0.706</v>
       </c>
       <c r="W45" t="n">
-        <v>1.444</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="X45" t="n">
-        <v>1.278</v>
+        <v>0.706</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.944</v>
+        <v>2.059</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.556</v>
+        <v>3.647</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.607</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.111</v>
+        <v>0.294</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.667</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.167</v>
+        <v>0.312</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.167</v>
+        <v>0.118</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.611</v>
+        <v>0.353</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.273</v>
+        <v>0.333</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.111</v>
+        <v>0.059</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.611</v>
+        <v>0.059</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.611</v>
+        <v>0.235</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.379</v>
+        <v>0.25</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>6.742</v>
+        <v>8.334</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.445</v>
+        <v>0.489</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.489</v>
+        <v>0.58</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.873</v>
+        <v>0.988</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.107</v>
+        <v>0.148</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.17</v>
+        <v>0.596</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.923</v>
+        <v>0.286</v>
       </c>
       <c r="AV45" t="n">
-        <v>7.692</v>
+        <v>4.238</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.615</v>
+        <v>4.524</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.18</v>
+        <v>0.196</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.112</v>
+        <v>0.129</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.029</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#12 R. MARTÍNEZ-QUINTANILLA JIMÉNEZ (Per Game)</t>
+          <t>#37 C. TOLEDO ZAMORA (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C46" t="n">
-        <v>3.92</v>
+        <v>9.038</v>
       </c>
       <c r="D46" t="n">
-        <v>0.36</v>
+        <v>2.962</v>
       </c>
       <c r="E46" t="n">
-        <v>1.12</v>
+        <v>5.423</v>
       </c>
       <c r="F46" t="n">
-        <v>1.04</v>
+        <v>0.346</v>
       </c>
       <c r="G46" t="n">
-        <v>3.24</v>
+        <v>1.615</v>
       </c>
       <c r="H46" t="n">
-        <v>0.08</v>
+        <v>2.077</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08</v>
+        <v>3.385</v>
       </c>
       <c r="J46" t="n">
-        <v>0.44</v>
+        <v>1.192</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>2.962</v>
       </c>
       <c r="L46" t="n">
-        <v>0.68</v>
+        <v>3.154</v>
       </c>
       <c r="M46" t="n">
-        <v>0.48</v>
+        <v>0.346</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>0.76</v>
+        <v>1.269</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.44</v>
+        <v>0.654</v>
       </c>
       <c r="R46" t="n">
-        <v>2.12</v>
+        <v>2.885</v>
       </c>
       <c r="S46" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="U46" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.654</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.462</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>0.2</v>
       </c>
-      <c r="V46" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.341</v>
-      </c>
       <c r="AK46" t="n">
-        <v>0.48</v>
+        <v>0.192</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.6</v>
+        <v>0.846</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.3</v>
+        <v>0.227</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>23:49</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>5.155</v>
+        <v>9.797000000000001</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.44</v>
+        <v>0.495</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.446</v>
+        <v>0.53</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.76</v>
+        <v>0.923</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.147</v>
+        <v>0.13</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.018</v>
+        <v>0.295</v>
       </c>
       <c r="AU46" t="n">
-        <v>0.579</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="AV46" t="n">
-        <v>5.737</v>
+        <v>5.545</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.316</v>
+        <v>6.485</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.179</v>
+        <v>0.185</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.049</v>
+        <v>0.124</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.082</v>
+        <v>0.133</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.018</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#13 P. PARRA GOMEZ (Per Game)</t>
+          <t>#88 J. TAVELLI (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C47" t="n">
-        <v>0.333</v>
+        <v>6.423</v>
       </c>
       <c r="D47" t="n">
-        <v>0.167</v>
+        <v>1.731</v>
       </c>
       <c r="E47" t="n">
-        <v>0.333</v>
+        <v>3.692</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2.423</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2.038</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>3.846</v>
       </c>
       <c r="K47" t="n">
-        <v>0.167</v>
+        <v>2.385</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="M47" t="n">
-        <v>0.167</v>
+        <v>1.538</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.333</v>
+        <v>1.654</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.333</v>
+        <v>0.423</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.769</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="U47" t="n">
-        <v>0.333</v>
+        <v>1.269</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="W47" t="n">
-        <v>0.333</v>
+        <v>1.077</v>
       </c>
       <c r="X47" t="n">
-        <v>0.167</v>
+        <v>0.654</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.167</v>
+        <v>1.077</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.333</v>
+        <v>1.923</v>
       </c>
       <c r="AA47" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB47" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.115</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>0.654</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.038</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>01:43</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0.667</v>
+        <v>8.666</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.5</v>
+        <v>0.406</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.5</v>
+        <v>0.458</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.5</v>
+        <v>0.741</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.5</v>
+        <v>0.191</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.326</v>
       </c>
       <c r="AV47" t="n">
-        <v>1</v>
+        <v>3.698</v>
       </c>
       <c r="AW47" t="n">
-        <v>1</v>
+        <v>6.023</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.173</v>
+        <v>0.202</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.102</v>
+        <v>0.133</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#14 H. KABASELE KASONGA (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C48" t="n">
-        <v>8.667</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>3.667</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>7.167</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.75</v>
+        <v>1.846</v>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>2.154</v>
       </c>
       <c r="M48" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.167</v>
+        <v>0.846</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.667</v>
+        <v>0.846</v>
       </c>
       <c r="R48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.583</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.646</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -8286,3353 +8031,383 @@
         <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
         <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>9.407</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.921</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>6.214</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>6.643</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#15 T. BOUNDI (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C49" t="n">
-        <v>0.75</v>
+        <v>73.73099999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0.125</v>
+        <v>17.462</v>
       </c>
       <c r="E49" t="n">
-        <v>0.125</v>
+        <v>37.923</v>
       </c>
       <c r="F49" t="n">
-        <v>0.125</v>
+        <v>7.962</v>
       </c>
       <c r="G49" t="n">
-        <v>0.25</v>
+        <v>29.192</v>
       </c>
       <c r="H49" t="n">
-        <v>0.125</v>
+        <v>14.923</v>
       </c>
       <c r="I49" t="n">
-        <v>0.25</v>
+        <v>22.269</v>
       </c>
       <c r="J49" t="n">
-        <v>0.125</v>
+        <v>15.385</v>
       </c>
       <c r="K49" t="n">
-        <v>0.75</v>
+        <v>24.692</v>
       </c>
       <c r="L49" t="n">
-        <v>0.125</v>
+        <v>14.962</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>7.538</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.346</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>13.769</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>5.846</v>
       </c>
       <c r="R49" t="n">
-        <v>0.625</v>
+        <v>23.615</v>
       </c>
       <c r="S49" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>8</v>
+        <v>1220</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>8.962</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>7.385</v>
       </c>
       <c r="W49" t="n">
-        <v>0.25</v>
+        <v>10.308</v>
       </c>
       <c r="X49" t="n">
-        <v>0.125</v>
+        <v>5.769</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>13.077</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>24.885</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>3.077</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>8.385</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>4.577</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.125</v>
+        <v>3.115</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.25</v>
+        <v>10.808</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.5</v>
+        <v>0.288</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>4.846</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>18.385</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>203:50</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0.485</v>
+        <v>90.68300000000001</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.833</v>
+        <v>0.438</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.773</v>
+        <v>0.479</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.546</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.117</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>4.874</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>5.992</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.038</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.257</v>
+        <v>0.13</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#21 G. MILADINOVIC (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>26</v>
       </c>
       <c r="C50" t="n">
+        <v>82.61499999999999</v>
+      </c>
+      <c r="D50" t="n">
+        <v>17.346</v>
+      </c>
+      <c r="E50" t="n">
+        <v>33.808</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10.154</v>
+      </c>
+      <c r="G50" t="n">
+        <v>30.038</v>
+      </c>
+      <c r="H50" t="n">
+        <v>17.462</v>
+      </c>
+      <c r="I50" t="n">
+        <v>25.846</v>
+      </c>
+      <c r="J50" t="n">
+        <v>15.192</v>
+      </c>
+      <c r="K50" t="n">
+        <v>28.615</v>
+      </c>
+      <c r="L50" t="n">
+        <v>13.308</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7.923</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="O50" t="n">
+        <v>62</v>
+      </c>
+      <c r="P50" t="n">
+        <v>14.269</v>
+      </c>
+      <c r="Q50" t="n">
         <v>6.731</v>
       </c>
-      <c r="D50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E50" t="n">
-        <v>5.577</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3.385</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O50" t="n">
-        <v>5</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.731</v>
-      </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
+        <v>21.269</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1653</v>
+      </c>
+      <c r="U50" t="n">
+        <v>9.538</v>
+      </c>
+      <c r="V50" t="n">
+        <v>7.192</v>
+      </c>
+      <c r="W50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="X50" t="n">
+        <v>6.038</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>12.192</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>22.231</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.154</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>5.038</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>10.038</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>6.538</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>203:50</t>
+        </is>
+      </c>
+      <c r="AO50" t="n">
+        <v>89.488</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AR50" t="n">
         <v>0.923</v>
       </c>
-      <c r="R50" t="n">
-        <v>2.731</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="T50" t="n">
-        <v>169</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.577</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.615</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>8.695</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0.774</v>
-      </c>
       <c r="AS50" t="n">
-        <v>0.199</v>
+        <v>0.159</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.511</v>
+        <v>1.065</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.467</v>
+        <v>4.474</v>
       </c>
       <c r="AW50" t="n">
-        <v>3.978</v>
+        <v>5.539</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.219</v>
+        <v>0.197</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.073</v>
+        <v>0.061</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.202</v>
+        <v>0.151</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.039</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>#22 M. GARCIA ROSELLO (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>13</v>
-      </c>
-      <c r="C51" t="n">
-        <v>8.615</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1.769</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3.154</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4.462</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.615</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="R51" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="T51" t="n">
-        <v>94</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.077</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>9.148</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.9419999999999999</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>9.417</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>#24 U. ZAMORA MAÑA (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>12</v>
-      </c>
-      <c r="C52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.417</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R52" t="n">
-        <v>2.083</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T52" t="n">
-        <v>78</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>21:38</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>4.773</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>#25 F. HERNANDEZ MARTINEZ (Per Game)</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>26</v>
-      </c>
-      <c r="C53" t="n">
-        <v>9.615</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.885</v>
-      </c>
-      <c r="E53" t="n">
-        <v>4.154</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G53" t="n">
-        <v>4.769</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.154</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.154</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.308</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="O53" t="n">
-        <v>12</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.577</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.654</v>
-      </c>
-      <c r="T53" t="n">
-        <v>188</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.731</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="W53" t="n">
-        <v>2.808</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.846</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.731</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>2.923</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>22:35</t>
-        </is>
-      </c>
-      <c r="AO53" t="n">
-        <v>11.888</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>5.659</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>6.585</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0.066</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>#26 M. MUKENDI MUKENDI (Per Game)</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>17</v>
-      </c>
-      <c r="C54" t="n">
-        <v>8.234999999999999</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.471</v>
-      </c>
-      <c r="E54" t="n">
-        <v>4.941</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="H54" t="n">
-        <v>3.118</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4.235</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.588</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="O54" t="n">
-        <v>4</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.824</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.412</v>
-      </c>
-      <c r="T54" t="n">
-        <v>149</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.118</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.059</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>3.647</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AO54" t="n">
-        <v>8.334</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>4.238</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>4.524</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>#88 J. TAVELLI (Per Game)</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>26</v>
-      </c>
-      <c r="C55" t="n">
-        <v>6.423</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.731</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3.692</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2.423</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2.038</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.846</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.385</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.538</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.654</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="R55" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="T55" t="n">
-        <v>207</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.885</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2.038</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>19:18</t>
-        </is>
-      </c>
-      <c r="AO55" t="n">
-        <v>8.666</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>2.326</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>3.698</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>6.023</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0.166</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>Equip (Per Game)</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>26</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO56" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>LOBE HUESCA LA MAGIA (Per Game)</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>13</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB (Per Game)</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>13</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>Equip (Per Game)</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>26</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="L59" t="n">
-        <v>2.154</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO (Per Game)</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>13</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB (Per Game)</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>13</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>CLASS BASQUET SANT ANTONI (Per Game)</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>13</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN (Per Game)</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>13</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>C.B. GETAFE (Per Game)</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>26</v>
-      </c>
-      <c r="C64" t="n">
-        <v>9.038</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2.962</v>
-      </c>
-      <c r="E64" t="n">
-        <v>5.423</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.615</v>
-      </c>
-      <c r="H64" t="n">
-        <v>2.077</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3.385</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3.385</v>
-      </c>
-      <c r="L64" t="n">
-        <v>2.731</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="O64" t="n">
-        <v>7</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.269</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="R64" t="n">
-        <v>2.885</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.962</v>
-      </c>
-      <c r="T64" t="n">
-        <v>269</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.308</v>
-      </c>
-      <c r="V64" t="n">
-        <v>2.462</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1.769</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.654</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>4.462</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>23:49</t>
-        </is>
-      </c>
-      <c r="AO64" t="n">
-        <v>9.797000000000001</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>5.545</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>6.485</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>0.054</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>BIELE ISB (Per Game)</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>13</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ (Per Game)</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>13</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>26</v>
-      </c>
-      <c r="C67" t="n">
-        <v>73.73099999999999</v>
-      </c>
-      <c r="D67" t="n">
-        <v>17.462</v>
-      </c>
-      <c r="E67" t="n">
-        <v>37.923</v>
-      </c>
-      <c r="F67" t="n">
-        <v>7.962</v>
-      </c>
-      <c r="G67" t="n">
-        <v>29.192</v>
-      </c>
-      <c r="H67" t="n">
-        <v>14.923</v>
-      </c>
-      <c r="I67" t="n">
-        <v>22.269</v>
-      </c>
-      <c r="J67" t="n">
-        <v>15.385</v>
-      </c>
-      <c r="K67" t="n">
-        <v>26.269</v>
-      </c>
-      <c r="L67" t="n">
-        <v>13.385</v>
-      </c>
-      <c r="M67" t="n">
-        <v>7.538</v>
-      </c>
-      <c r="N67" t="n">
-        <v>2.346</v>
-      </c>
-      <c r="O67" t="n">
-        <v>57</v>
-      </c>
-      <c r="P67" t="n">
-        <v>13.769</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>5.846</v>
-      </c>
-      <c r="R67" t="n">
-        <v>23.615</v>
-      </c>
-      <c r="S67" t="n">
-        <v>20.846</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1761</v>
-      </c>
-      <c r="U67" t="n">
-        <v>9.885</v>
-      </c>
-      <c r="V67" t="n">
-        <v>10.962</v>
-      </c>
-      <c r="W67" t="n">
-        <v>13.308</v>
-      </c>
-      <c r="X67" t="n">
-        <v>14.038</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>13.077</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>24.885</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>3.077</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>8.385</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>4.577</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>3.115</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>10.808</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>4.846</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>18.385</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>203:50</t>
-        </is>
-      </c>
-      <c r="AO67" t="n">
-        <v>90.68300000000001</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>4.874</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>5.992</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>26</v>
-      </c>
-      <c r="C68" t="n">
-        <v>82.61499999999999</v>
-      </c>
-      <c r="D68" t="n">
-        <v>17.346</v>
-      </c>
-      <c r="E68" t="n">
-        <v>33.808</v>
-      </c>
-      <c r="F68" t="n">
-        <v>10.154</v>
-      </c>
-      <c r="G68" t="n">
-        <v>30.038</v>
-      </c>
-      <c r="H68" t="n">
-        <v>17.462</v>
-      </c>
-      <c r="I68" t="n">
-        <v>25.846</v>
-      </c>
-      <c r="J68" t="n">
-        <v>15.192</v>
-      </c>
-      <c r="K68" t="n">
-        <v>29.846</v>
-      </c>
-      <c r="L68" t="n">
-        <v>12.077</v>
-      </c>
-      <c r="M68" t="n">
-        <v>7.923</v>
-      </c>
-      <c r="N68" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="O68" t="n">
-        <v>61</v>
-      </c>
-      <c r="P68" t="n">
-        <v>14.269</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>6.731</v>
-      </c>
-      <c r="R68" t="n">
-        <v>21.269</v>
-      </c>
-      <c r="S68" t="n">
-        <v>23.192</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2257</v>
-      </c>
-      <c r="U68" t="n">
-        <v>11.192</v>
-      </c>
-      <c r="V68" t="n">
-        <v>10.692</v>
-      </c>
-      <c r="W68" t="n">
-        <v>15.077</v>
-      </c>
-      <c r="X68" t="n">
-        <v>16.308</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>12.192</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>22.231</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>2.962</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>2.154</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>5.038</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>3.615</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>10.038</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>6.538</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>20</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>203:50</t>
-        </is>
-      </c>
-      <c r="AO68" t="n">
-        <v>89.488</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>4.474</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>5.539</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="BA68" t="n">
         <v>0</v>
       </c>
     </row>
